--- a/bioinformatics-analysis/resources/sample-meta-en.xlsx
+++ b/bioinformatics-analysis/resources/sample-meta-en.xlsx
@@ -1,133 +1,94 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\private\bioinfo-view\bio2023\code\bioinfo-view-be\bioinformatics-analysis\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AAA2BEE-F3C4-4BE4-B1EF-41F06006F3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="27096" windowHeight="16296" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="27096" windowHeight="16296" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1" concurrentCalc="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Sampling Date(YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>Submission Date(YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>Sampling Site</t>
-  </si>
-  <si>
-    <t>Sample Type</t>
-  </si>
-  <si>
-    <t>Tumor Content</t>
-  </si>
-  <si>
-    <t>Tumor Sample</t>
-  </si>
-  <si>
-    <t>Patient Identification</t>
-  </si>
-  <si>
-    <t>Sampling Tube Brand</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Specimen Type</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="10">
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <sz val="21"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="21"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18.850000000000001"/>
-      <color theme="1"/>
       <name val="Material Icons"/>
       <family val="1"/>
-    </font>
-    <font>
+      <color theme="1"/>
+      <sz val="18.85"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="24"/>
-      <color theme="1"/>
       <name val="Material Icons"/>
       <family val="1"/>
-    </font>
-    <font>
+      <color theme="1"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="11"/>
-      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
       <family val="3"/>
-      <charset val="134"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -143,52 +104,112 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -449,143 +470,141 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.77734375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="24.6640625" customWidth="1"/>
-    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col width="24.6640625" customWidth="1" style="9" min="1" max="2"/>
+    <col width="20" bestFit="1" customWidth="1" style="9" min="7" max="7"/>
+    <col width="20.6640625" bestFit="1" customWidth="1" style="9" min="8" max="8"/>
+    <col width="14.77734375" bestFit="1" customWidth="1" style="9" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="26.4">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" ht="23.4">
-      <c r="A9" s="3"/>
-    </row>
-    <row r="11" spans="1:9" ht="20.399999999999999">
-      <c r="A11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" ht="30.6">
-      <c r="A12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" ht="20.399999999999999">
-      <c r="A13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" ht="30.6">
-      <c r="A14" s="5"/>
-    </row>
-    <row r="15" spans="1:9" ht="20.399999999999999">
-      <c r="A15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" ht="20.399999999999999">
-      <c r="A16" s="4"/>
-    </row>
-    <row r="17" spans="1:1" ht="30.6">
-      <c r="A17" s="5"/>
-    </row>
-    <row r="18" spans="1:1" ht="20.399999999999999">
-      <c r="A18" s="4"/>
-    </row>
-    <row r="20" spans="1:1" ht="20.399999999999999">
-      <c r="A20" s="4"/>
-    </row>
-    <row r="21" spans="1:1" ht="20.399999999999999">
-      <c r="A21" s="4"/>
-    </row>
-    <row r="22" spans="1:1" ht="20.399999999999999">
-      <c r="A22" s="4"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sampling Date(YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Submission Date(YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sampling Site</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Sample Type</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Tumor Content</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Tumor Sample</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>NC Sample</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Tag Label</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Patient Identification</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>Sampling Tube Brand</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>Specimen Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="26.4" customHeight="1" s="9">
+      <c r="A8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="23.4" customHeight="1" s="9">
+      <c r="A9" s="3" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="20.4" customHeight="1" s="9">
+      <c r="A11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="30.6" customHeight="1" s="9">
+      <c r="A12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="20.4" customHeight="1" s="9">
+      <c r="A13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="30.6" customHeight="1" s="9">
+      <c r="A14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="20.4" customHeight="1" s="9">
+      <c r="A15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="20.4" customHeight="1" s="9">
+      <c r="A16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="30.6" customHeight="1" s="9">
+      <c r="A17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="20.4" customHeight="1" s="9">
+      <c r="A18" s="4" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="20.4" customHeight="1" s="9">
+      <c r="A20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="20.4" customHeight="1" s="9">
+      <c r="A21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="20.4" customHeight="1" s="9">
+      <c r="A22" s="4" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation sqref="D1:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"FFPE,Fresh Tissue,Blood,Cerebrospinal Fluid,Pleural Effusion,Other Body Fluids,Bone Marrow"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Arial"&amp;10&amp;K000000 Internal</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Arial"&amp;10 &amp;K000000_x000d_# Internal</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <pixelatorList sheetStid="1"/>
-  <pixelatorList sheetStid="2"/>
-</pixelators>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<woProps xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <woSheetsProps>
-    <woSheetProps sheetStid="1" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
-      <cellprotection/>
-      <appEtDbRelations/>
-    </woSheetProps>
-  </woSheetsProps>
-  <woBookProps>
-    <bookSettings isFilterShared="1" coreConquerUserId="" isAutoUpdatePaused="0" filterType="conn" isMergeTasksAutoUpdate="0" isInserPicAsAttachment="0"/>
-  </woBookProps>
-</woProps>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{06530cf4-8573-4c29-a912-bbcdac835909}" enabled="1" method="Standard" siteId="{ecaa386b-c8df-4ce0-ad01-740cbdb5ba55}" contentBits="2" removed="0"/>
-</clbl:labelList>
 </file>
--- a/bioinformatics-analysis/resources/sample-meta-en.xlsx
+++ b/bioinformatics-analysis/resources/sample-meta-en.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="27096" windowHeight="16296" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1" concurrentCalc="0"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.77734375" defaultRowHeight="13.8"/>
   <cols>
     <col width="24.6640625" customWidth="1" style="9" min="1" max="2"/>
@@ -520,22 +520,17 @@
           <t>NC Sample</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>Tag Label</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Patient Identification</t>
         </is>
       </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>Sampling Tube Brand</t>
+        </is>
+      </c>
       <c r="J1" s="8" t="inlineStr">
-        <is>
-          <t>Sampling Tube Brand</t>
-        </is>
-      </c>
-      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Specimen Type</t>
         </is>
@@ -590,10 +585,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F1048576" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation sqref="D1:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D1:D1048576" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>"FFPE,Fresh Tissue,Blood,Cerebrospinal Fluid,Pleural Effusion,Other Body Fluids,Bone Marrow"</formula1>
     </dataValidation>
   </dataValidations>
